--- a/mahbinasayi.xlsx
+++ b/mahbinasayi.xlsx
@@ -3258,6 +3258,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I960"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
